--- a/data/credit_bond_2026-08-31.xlsx
+++ b/data/credit_bond_2026-08-31.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-08-31" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-01" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -163,257 +163,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-31</t>
+          <t>数据来源：DM    2026-09-01</t>
         </is>
       </c>
     </row>

--- a/data/credit_bond_2026-08-31.xlsx
+++ b/data/credit_bond_2026-08-31.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-01" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-02" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -163,257 +163,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
     </row>

--- a/data/credit_bond_2026-08-31.xlsx
+++ b/data/credit_bond_2026-08-31.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-02" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-03" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -163,257 +163,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-02</t>
+          <t>数据来源：DM    2026-09-03</t>
         </is>
       </c>
     </row>

--- a/data/credit_bond_2026-08-31.xlsx
+++ b/data/credit_bond_2026-08-31.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-03" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-04" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -163,257 +163,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-03</t>
+          <t>数据来源：DM    2026-09-04</t>
         </is>
       </c>
     </row>
